--- a/rich_v2_autotest/迭代三测试资料包/第一组_大富翁统一测试用例_迭代三_精简修正版.xlsx
+++ b/rich_v2_autotest/迭代三测试资料包/第一组_大富翁统一测试用例_迭代三_精简修正版.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A1-A21_测试用例汇总" sheetId="1" r:id="R483d0f227b5d4a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A1-A21_测试用例汇总" sheetId="1" r:id="R8ba491d6ff9f4b52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1532,7 +1532,7 @@
         <x:v>明确显示最终采用值30000并直接进入角色组合选择，不等待二次确认</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="48" hidden="0" customHeight="1">
+    <x:row r="25" ht="46" hidden="0" customHeight="1">
       <x:c r="A25" s="12" t="str">
         <x:v>A4 回合控制与落点处理</x:v>
       </x:c>
@@ -1546,7 +1546,8 @@
 4. 下一玩家A</x:v>
       </x:c>
       <x:c r="D25" s="14" t="str">
-        <x:v>进入Q的回合</x:v>
+        <x:v>1. Q执行STEP 1
+2. 出现购买提示后输入N</x:v>
       </x:c>
       <x:c r="E25" s="14" t="str">
         <x:v>1. Q可正常输入掷骰前命令和Roll
@@ -5238,7 +5239,7 @@
 3. 保留回合数按规则更新</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" ht="36" hidden="0" customHeight="1">
+    <x:row r="183" ht="58" hidden="0" customHeight="1">
       <x:c r="A183" s="12" t="str">
         <x:v>A14 财神随机出现与获取</x:v>
       </x:c>
@@ -5251,7 +5252,9 @@
 3. 两人此前均无财神状态</x:v>
       </x:c>
       <x:c r="D183" s="14" t="str">
-        <x:v>Q与A依次移动经过F所在格</x:v>
+        <x:v>1. Q执行STEP 2
+2. 购买提示输入N
+3. A执行STEP 3</x:v>
       </x:c>
       <x:c r="E183" s="14" t="str">
         <x:v>1. Q作为第一个经过者获得财神
@@ -8363,7 +8366,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d8bd4957be14abb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc15e7a1072a44749"/>
   </x:tableParts>
 </x:worksheet>
 </file>